--- a/satisfaction_surveys/022_selfie_perception_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/022_selfie_perception_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -531,30 +531,30 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>selfie_frequency</t>
+          <t>selfie_reason</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How Often Do You Take Selfies</t>
+          <t>Why Do You Take Selfies</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>selfie_reason</t>
+          <t>selfie_device</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Why Do You Take Selfies</t>
+          <t>What Device Do You Use To Take Selfies</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>selfie_image</t>
+          <t>selfie_location</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Selfie Image</t>
+          <t>Where Do You Take Selfies</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>selfie_emotions</t>
+          <t>selfie_image</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What Emotions Do You Feel When You Take Selfies</t>
+          <t>What Image Do You Use For Selfie</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>selfie_frequency_time</t>
+          <t>selfie_share</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How Often Do You Take Selfies</t>
+          <t>How Do You Share Selfies</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>selfie_device</t>
+          <t>selfie_view</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What Device Do You Use To Take Selfies</t>
+          <t>How Do You View Yourself In Selfies</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>selfie_location</t>
+          <t>selfie_perception</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Where Do You Take Selfies</t>
+          <t>How Do You Perceive Yourself In Selfies</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,115 +699,115 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>selfie_social_media</t>
+          <t>selfie_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Why Do You Share Selfies</t>
+          <t>How Many Selfies Do You Take Per Week</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>selfie_self_image</t>
+          <t>selfie_average_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How Do You View Yourself</t>
+          <t>Average Time Spent On Selfies</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>selfie_perception</t>
+          <t>selfie_frequency_of_taken_selfies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How Do You Perceive Yourself</t>
+          <t>Average Number Of Selfies Taken Per Week</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>selfie_frequency_of_selfies_taken</t>
+          <t>selfie_feeling</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How Many Selfies Do You Take Per Week</t>
+          <t>How Do You Feel When You Take Selfies</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>selfie_average_selfie_per_week</t>
+          <t>selfie_sharing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What Is The Average Number Of Selfies You Take Per Week</t>
+          <t>Selfie Sharing</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_feel</t>
+          <t>selfie_perceiving</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How Do You Feel When You Take Selfies</t>
+          <t>How Do You Perceive Selfies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_share</t>
+          <t>selfie_device_used</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How Do You Share Selfies</t>
+          <t>Selfie Device Used</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>selfie_perception_selfie</t>
+          <t>selfie_location_taken</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How Do You Perceive Selfies</t>
+          <t>Selfie Location Taken</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>selfie_image_selfie</t>
+          <t>selfie_image_used</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What Image Do You Use For Selfie</t>
+          <t>Selfie Image Used</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,570 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_perceive_selfie</t>
+          <t>selfie_sharing_selfies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How Do You Perceive Selfie</t>
+          <t>Selfie Sharing Selfies</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>selfie_selfie_frequency</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Selfie Frequency</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>selfie_perception_of_selfie</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Perception Of Selfie</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>selfie_selfie_device</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Selfie Device</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>selfie_selfie_time</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Selfie Time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>selfie_selfie_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Selfie Date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>selfie_selfie_location</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Selfie Location</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>selfie_selfie_other</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>selfie_selfie_note</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>selfie_selfie_email</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Selfie Email</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>selfie_selfie_phone</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Selfie Phone</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>selfie_selfie_note</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>selfie_selfie_file</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Selfie File</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>selfie_selfie_phone</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Selfie Phone</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>selfie_selfie_email</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Selfie Email</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>selfie_selfie_note</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>selfie_selfie_time</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>selfie_selfie_phone</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>selfie_selfie_email</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>selfie_selfie_note</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>selfie_selfie_file</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>selfie_selfie_phone</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>selfie_selfie_email</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>selfie_selfie_note</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>selfie_selfie_file</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1489,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1517,126 +965,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>selfie_reason_choices</t>
+          <t>selfie_habits_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>i_am_trying_to_look_good</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>I am trying to look good</t>
+          <t>Frequent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>selfie_reason_choices</t>
+          <t>selfie_habits_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>i_am_trying_to_feel_good</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>I am trying to feel good</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>selfie_reason_choices</t>
+          <t>selfie_habits_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>i_am_trying_to_share_with_friends</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>I am trying to share with friends</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>selfie_reason_choices</t>
+          <t>selfie_habits_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other,_please_specify</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other, please specify</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>selfie_image_choices</t>
+          <t>selfie_reason_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>a_picture_of_myself_in_a_formal_setting</t>
+          <t>to_feel_good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A picture of myself in a formal setting</t>
+          <t>To feel good</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>selfie_image_choices</t>
+          <t>selfie_reason_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>a_picture_of_myself_in_an_informal_setting</t>
+          <t>to_share_with_friends</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A picture of myself in an informal setting</t>
+          <t>To share with friends</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>selfie_image_choices</t>
+          <t>selfie_reason_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>a_picture_of_myself_with_friends</t>
+          <t>to_document_memories</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A picture of myself with friends</t>
+          <t>To document memories</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>selfie_image_choices</t>
+          <t>selfie_reason_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1653,58 +1101,58 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>selfie_emotions_choices</t>
+          <t>selfie_device_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>selfie_emotions_choices</t>
+          <t>selfie_device_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bored</t>
+          <t>camera</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bored</t>
+          <t>Camera</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>selfie_emotions_choices</t>
+          <t>selfie_device_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>anxious</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Anxious</t>
+          <t>Computer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>selfie_emotions_choices</t>
+          <t>selfie_device_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1721,58 +1169,58 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>selfie_device_choices</t>
+          <t>selfie_location_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>smartphone</t>
+          <t>at_home</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>At home</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>selfie_device_choices</t>
+          <t>selfie_location_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>camera</t>
+          <t>at_work</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>At work</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>selfie_device_choices</t>
+          <t>selfie_location_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>on_vacation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Computer</t>
+          <t>On vacation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>selfie_device_choices</t>
+          <t>selfie_location_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1789,58 +1237,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>selfie_location_choices</t>
+          <t>selfie_image_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>at_home</t>
+          <t>a_picture_of_myself</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>At home</t>
+          <t>A picture of myself</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>selfie_location_choices</t>
+          <t>selfie_image_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>at_work</t>
+          <t>a_picture_of_my_friends</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>At work</t>
+          <t>A picture of my friends</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>selfie_location_choices</t>
+          <t>selfie_image_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>on_vacation</t>
+          <t>a_picture_of_my_family</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>On vacation</t>
+          <t>A picture of my family</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>selfie_location_choices</t>
+          <t>selfie_image_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1857,7 +1305,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>selfie_social_media_choices</t>
+          <t>selfie_share_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1874,7 +1322,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>selfie_social_media_choices</t>
+          <t>selfie_share_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1891,7 +1339,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>selfie_social_media_choices</t>
+          <t>selfie_share_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1908,7 +1356,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>selfie_social_media_choices</t>
+          <t>selfie_share_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1925,7 +1373,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>selfie_self_image_choices</t>
+          <t>selfie_view_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1942,7 +1390,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>selfie_self_image_choices</t>
+          <t>selfie_view_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1959,7 +1407,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>selfie_self_image_choices</t>
+          <t>selfie_view_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1976,7 +1424,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>selfie_self_image_choices</t>
+          <t>selfie_view_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1998,12 +1446,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>attractive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Attractive</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -2015,12 +1463,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -2032,12 +1480,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>unattractive</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Unattractive</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2061,7 +1509,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_feel_choices</t>
+          <t>selfie_feeling_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2078,7 +1526,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_feel_choices</t>
+          <t>selfie_feeling_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2095,7 +1543,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_feel_choices</t>
+          <t>selfie_feeling_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2112,7 +1560,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_feel_choices</t>
+          <t>selfie_feeling_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2129,7 +1577,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_share_choices</t>
+          <t>selfie_sharing_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2146,7 +1594,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_share_choices</t>
+          <t>selfie_sharing_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2163,7 +1611,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_share_choices</t>
+          <t>selfie_sharing_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2180,7 +1628,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_share_choices</t>
+          <t>selfie_sharing_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2197,7 +1645,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>selfie_perception_selfie_choices</t>
+          <t>selfie_perceiving_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2214,7 +1662,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>selfie_perception_selfie_choices</t>
+          <t>selfie_perceiving_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2231,7 +1679,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>selfie_perception_selfie_choices</t>
+          <t>selfie_perceiving_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2248,7 +1696,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>selfie_perception_selfie_choices</t>
+          <t>selfie_perceiving_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2265,58 +1713,58 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>selfie_image_selfie_choices</t>
+          <t>selfie_device_used_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>a_picture_of_myself</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>A picture of myself</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>selfie_image_selfie_choices</t>
+          <t>selfie_device_used_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>a_picture_of_my_friends</t>
+          <t>camera</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A picture of my friends</t>
+          <t>Camera</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>selfie_image_selfie_choices</t>
+          <t>selfie_device_used_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>a_picture_of_my_family</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A picture of my family</t>
+          <t>Computer</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>selfie_image_selfie_choices</t>
+          <t>selfie_device_used_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2333,58 +1781,58 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_perceive_selfie_choices</t>
+          <t>selfie_location_taken_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>beautiful</t>
+          <t>at_home</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Beautiful</t>
+          <t>At home</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_perceive_selfie_choices</t>
+          <t>selfie_location_taken_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ugly</t>
+          <t>at_work</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ugly</t>
+          <t>At work</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_perceive_selfie_choices</t>
+          <t>selfie_location_taken_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>on_vacation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>On vacation</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>selfie_how_do_you_perceive_selfie_choices</t>
+          <t>selfie_location_taken_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2401,58 +1849,58 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>selfie_perception_of_selfie_choices</t>
+          <t>selfie_image_used_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>a_picture_of_myself</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>A picture of myself</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>selfie_perception_of_selfie_choices</t>
+          <t>selfie_image_used_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>a_picture_of_my_friends</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>A picture of my friends</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>selfie_perception_of_selfie_choices</t>
+          <t>selfie_image_used_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>a_picture_of_my_family</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>A picture of my family</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>selfie_perception_of_selfie_choices</t>
+          <t>selfie_image_used_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2469,58 +1917,58 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>selfie_selfie_device_choices</t>
+          <t>selfie_sharing_selfies_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>smartphone</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>selfie_selfie_device_choices</t>
+          <t>selfie_sharing_selfies_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>camera</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>selfie_selfie_device_choices</t>
+          <t>selfie_sharing_selfies_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Computer</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>selfie_selfie_device_choices</t>
+          <t>selfie_sharing_selfies_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2529,210 +1977,6 @@
         </is>
       </c>
       <c r="C61" t="inlineStr">
-        <is>
-          <t>Other, please specify</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>selfie_selfie_location_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>at_home</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>At home</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>selfie_selfie_location_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>at_work</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>At work</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>selfie_selfie_location_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>on_vacation</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>On vacation</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>selfie_selfie_location_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>other,_please_specify</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Other, please specify</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>selfie_selfie_phone_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>mobile</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>selfie_selfie_phone_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>desktop</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Desktop</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>selfie_selfie_phone_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>laptop</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>selfie_selfie_phone_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>other,_please_specify</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Other, please specify</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>selfie_selfie_email_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>mobile</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>selfie_selfie_email_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>desktop</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Desktop</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>selfie_selfie_email_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>laptop</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>selfie_selfie_email_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>other,_please_specify</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
         <is>
           <t>Other, please specify</t>
         </is>
